--- a/backend/temp/exports/Activity_Reports_Export.xlsx
+++ b/backend/temp/exports/Activity_Reports_Export.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -774,6 +774,384 @@
       <c r="AA3" s="3" t="inlineStr"/>
       <c r="AB3" s="3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Program</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Vibrant and enriching campus experience</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Societal (Law Abiding)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Session</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>An Awareness session on Cybercrime</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>27th February,2026</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>12.45PM- 1.45PM</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Room 044, Ground Floor, RnD, Christ (Deemed to be University) Bengaluru- 560029</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>G. Krishnendu (2441421)</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Student of Department of Statistics and Data Science</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>An Awareness session on Cybercrime</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Students and Faculties</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>Expert-Led Legal Insight: The session was conducted by Dr. Diya C R, Assistant Professor, School of Law, who provided a comprehensive overview of cybercrime from a legal perspective. Real-World Cybercrime Cases: The discussion included commonly occurring cyber offences such as phishing attacks, online banking frauds, UPI scams, identity theft, fake job offers, social media hacking, and misuse of OTPs, explained with practical examples. Understanding Legal Frameworks: The session highlighted important cyber laws in India, including provisions under the Information Technology Act, and explained the legal remedies available to victims. Practical Cyber Safety Measures: Clear guidelines were provided on safe digital practices, recognizing fraudulent links and calls, protecting personal data, and steps to take if one becomes a victim of cybercrime. Role of Cyber Security: A clear explanation about the role of cyber security in dealing with cyber crime was discussed by the speaker. The role of digital proof was especially discussed.</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>To create awareness about different types of cybercrimes and their increasing impact on individuals and society. To help participants understand the legal implications and rights related to cyber offences. To encourage responsible digital behavior and safe online practices. To emphasize the importance of not sharing sensitive information such as OTPs, passwords, PINs, or personal details with unknown sources. To equip students and faculty with knowledge on preventive measures and reporting mechanisms in case of cyber fraud.</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>The awareness session on Cybercrime was conducted by Dr. Diya C R, Assistant Professor, School of Law, to educate participants about the growing threats in the digital world and the legal aspects associated with cyber offences. The session focused on common cybercrimes such as phishing, online fraud, UPI scams, identity theft, and misuse of personal information. Through real-life examples and clear explanations, participants gained a better understanding of cyber laws, preventive measures, and responsible digital behavior. The interactive discussion enhanced awareness and empowered attendees to identify, prevent, and respond effectively to cyber threats, promoting safer and more secure use of digital platforms.</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Program</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Vibrant and enriching campus experience</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Societal (Law Abiding)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Session</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>An Awareness session on Cybercrime</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>27th February,2026</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>12.45PM- 1.45PM</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Room 044, Ground Floor, RnD, Christ (Deemed to be University) Bengaluru- 560029</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>G. Krishnendu (2441421)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Student of Department of Statistics and Data Science</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>An Awareness session on Cybercrime</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Students and Faculties</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>Expert-Led Legal Insight: The session was conducted by Dr. Diya C R, Assistant Professor, School of Law, who provided a comprehensive overview of cybercrime from a legal perspective. Real-World Cybercrime Cases: The discussion included commonly occurring cyber offences such as phishing attacks, online banking frauds, UPI scams, identity theft, fake job offers, social media hacking, and misuse of OTPs, explained with practical examples. Understanding Legal Frameworks: The session highlighted important cyber laws in India, including provisions under the Information Technology Act, and explained the legal remedies available to victims. Practical Cyber Safety Measures: Clear guidelines were provided on safe digital practices, recognizing fraudulent links and calls, protecting personal data, and steps to take if one becomes a victim of cybercrime. Role of Cyber Security: A clear explanation about the role of cyber security in dealing with cyber crime was discussed by the speaker. The role of digital proof was especially discussed.</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>To create awareness about different types of cybercrimes and their increasing impact on individuals and society. To help participants understand the legal implications and rights related to cyber offences. To encourage responsible digital behavior and safe online practices. To emphasize the importance of not sharing sensitive information such as OTPs, passwords, PINs, or personal details with unknown sources. To equip students and faculty with knowledge on preventive measures and reporting mechanisms in case of cyber fraud.</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>The awareness session on Cybercrime was conducted by Dr. Diya C R, Assistant Professor, School of Law, to educate participants about the growing threats in the digital world and the legal aspects associated with cyber offences. The session focused on common cybercrimes such as phishing, online fraud, UPI scams, identity theft, and misuse of personal information. Through real-life examples and clear explanations, participants gained a better understanding of cyber laws, preventive measures, and responsible digital behavior. The interactive discussion enhanced awareness and empowered attendees to identify, prevent, and respond effectively to cyber threats, promoting safer and more secure use of digital platforms.</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Program</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Vibrant and enriching campus experience</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Societal (Law Abiding)</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Session</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>An Awareness session on Cybercrime</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>27th February,2026</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>12.45PM- 1.45PM</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Room 044, Ground Floor, RnD, Christ (Deemed to be University) Bengaluru- 560029</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>G. Krishnendu (2441421)</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>Student of Department of Statistics and Data Science</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>Christ University</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>An Awareness session on Cybercrime</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Students and Faculties</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>Expert-Led Legal Insight: The session was conducted by Dr. Diya C R, Assistant Professor, School of Law, who provided a comprehensive overview of cybercrime from a legal perspective. Real-World Cybercrime Cases: The discussion included commonly occurring cyber offences such as phishing attacks, online banking frauds, UPI scams, identity theft, fake job offers, social media hacking, and misuse of OTPs, explained with practical examples. Understanding Legal Frameworks: The session highlighted important cyber laws in India, including provisions under the Information Technology Act, and explained the legal remedies available to victims. Practical Cyber Safety Measures: Clear guidelines were provided on safe digital practices, recognizing fraudulent links and calls, protecting personal data, and steps to take if one becomes a victim of cybercrime. Role of Cyber Security: A clear explanation about the role of cyber security in dealing with cyber crime was discussed by the speaker. The role of digital proof was especially discussed.</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>To create awareness about different types of cybercrimes and their increasing impact on individuals and society. To help participants understand the legal implications and rights related to cyber offences. To encourage responsible digital behavior and safe online practices. To emphasize the importance of not sharing sensitive information such as OTPs, passwords, PINs, or personal details with unknown sources. To equip students and faculty with knowledge on preventive measures and reporting mechanisms in case of cyber fraud.</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>The awareness session on Cybercrime was conducted by Dr. Diya C R, Assistant Professor, School of Law, to educate participants about the growing threats in the digital world and the legal aspects associated with cyber offences. The session focused on common cybercrimes such as phishing, online fraud, UPI scams, identity theft, and misuse of personal information. Through real-life examples and clear explanations, participants gained a better understanding of cyber laws, preventive measures, and responsible digital behavior. The interactive discussion enhanced awareness and empowered attendees to identify, prevent, and respond effectively to cyber threats, promoting safer and more secure use of digital platforms.</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
